--- a/artfynd/A 20904-2026 artfynd.xlsx
+++ b/artfynd/A 20904-2026 artfynd.xlsx
@@ -8184,7 +8184,7 @@
         <v>134287393</v>
       </c>
       <c r="B75" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>134287396</v>
       </c>
       <c r="B76" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 20904-2026 artfynd.xlsx
+++ b/artfynd/A 20904-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126091089</v>
+        <v>126091011</v>
       </c>
       <c r="B2" t="n">
-        <v>80147</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557054</v>
+        <v>557066</v>
       </c>
       <c r="R2" t="n">
-        <v>7227146</v>
+        <v>7227351</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,45 +776,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091009</v>
+        <v>126091021</v>
       </c>
       <c r="B3" t="n">
-        <v>80182</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556917</v>
+        <v>557035</v>
       </c>
       <c r="R3" t="n">
         <v>7227275</v>
@@ -858,7 +855,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -881,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091030</v>
+        <v>126091022</v>
       </c>
       <c r="B4" t="n">
-        <v>57684</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -892,42 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557050</v>
+        <v>557054</v>
       </c>
       <c r="R4" t="n">
-        <v>7227253</v>
+        <v>7227356</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +948,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126091092</v>
+        <v>126091025</v>
       </c>
       <c r="B5" t="n">
-        <v>80050</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556906</v>
+        <v>556986</v>
       </c>
       <c r="R5" t="n">
-        <v>7227086</v>
+        <v>7227133</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126091099</v>
+        <v>126091122</v>
       </c>
       <c r="B6" t="n">
-        <v>98394</v>
+        <v>92283</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220093</v>
+        <v>2063</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1131,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557073</v>
+        <v>556726</v>
       </c>
       <c r="R6" t="n">
-        <v>7227326</v>
+        <v>7227064</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,12 +1144,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,7 +1158,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1198,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126091117</v>
+        <v>126091059</v>
       </c>
       <c r="B7" t="n">
-        <v>57840</v>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1209,34 +1191,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103022</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556827</v>
+        <v>556914</v>
       </c>
       <c r="R7" t="n">
-        <v>7227124</v>
+        <v>7227278</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1263,12 +1252,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,6 +1266,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1299,45 +1289,52 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126091170</v>
+        <v>126091060</v>
       </c>
       <c r="B8" t="n">
-        <v>80181</v>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556915</v>
+        <v>556945</v>
       </c>
       <c r="R8" t="n">
-        <v>7227293</v>
+        <v>7227306</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,6 +1375,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1400,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126091087</v>
+        <v>126091061</v>
       </c>
       <c r="B9" t="n">
-        <v>80147</v>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,16 +1427,23 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556869</v>
+        <v>557049</v>
       </c>
       <c r="R9" t="n">
-        <v>7227096</v>
+        <v>7227144</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,6 +1484,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1501,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126091080</v>
+        <v>126091075</v>
       </c>
       <c r="B10" t="n">
-        <v>80147</v>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1536,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556915</v>
+        <v>556792</v>
       </c>
       <c r="R10" t="n">
-        <v>7227290</v>
+        <v>7227253</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126091138</v>
+        <v>126091077</v>
       </c>
       <c r="B11" t="n">
-        <v>91389</v>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1613,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557073</v>
+        <v>556902</v>
       </c>
       <c r="R11" t="n">
-        <v>7227154</v>
+        <v>7227281</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1667,12 +1673,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1703,32 +1709,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126091058</v>
+        <v>126091078</v>
       </c>
       <c r="B12" t="n">
-        <v>98511</v>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1738,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557128</v>
+        <v>556918</v>
       </c>
       <c r="R12" t="n">
-        <v>7227190</v>
+        <v>7227271</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,12 +1774,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1804,32 +1810,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126091055</v>
+        <v>126091079</v>
       </c>
       <c r="B13" t="n">
-        <v>98511</v>
+        <v>80433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1839,10 +1845,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>556990</v>
+        <v>556916</v>
       </c>
       <c r="R13" t="n">
-        <v>7227108</v>
+        <v>7227278</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1869,12 +1875,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1905,10 +1911,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091118</v>
+        <v>126091080</v>
       </c>
       <c r="B14" t="n">
-        <v>57840</v>
+        <v>80433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1916,21 +1922,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103022</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1940,10 +1946,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556859</v>
+        <v>556915</v>
       </c>
       <c r="R14" t="n">
-        <v>7227119</v>
+        <v>7227290</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1970,12 +1976,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2006,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126091159</v>
+        <v>126091081</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>80433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,21 +2023,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2047,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557055</v>
+        <v>556946</v>
       </c>
       <c r="R15" t="n">
-        <v>7227102</v>
+        <v>7227279</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,12 +2077,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2107,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126091083</v>
+        <v>126091082</v>
       </c>
       <c r="B16" t="n">
-        <v>80147</v>
+        <v>80433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,7 +2148,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556975</v>
+        <v>556947</v>
       </c>
       <c r="R16" t="n">
         <v>7227303</v>
@@ -2208,32 +2214,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091112</v>
+        <v>126091083</v>
       </c>
       <c r="B17" t="n">
-        <v>57788</v>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2243,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556726</v>
+        <v>556975</v>
       </c>
       <c r="R17" t="n">
-        <v>7227088</v>
+        <v>7227303</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,12 +2279,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2309,10 +2315,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091157</v>
+        <v>126091084</v>
       </c>
       <c r="B18" t="n">
-        <v>79043</v>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2320,21 +2326,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2344,10 +2350,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556844</v>
+        <v>556737</v>
       </c>
       <c r="R18" t="n">
-        <v>7227129</v>
+        <v>7227192</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2380,11 +2386,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2415,32 +2416,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126091047</v>
+        <v>126091085</v>
       </c>
       <c r="B19" t="n">
-        <v>80175</v>
+        <v>80433</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2450,10 +2451,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556947</v>
+        <v>556709</v>
       </c>
       <c r="R19" t="n">
-        <v>7227277</v>
+        <v>7227134</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2480,12 +2481,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2516,10 +2517,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126091088</v>
+        <v>126091086</v>
       </c>
       <c r="B20" t="n">
-        <v>80147</v>
+        <v>80433</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2551,10 +2552,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557057</v>
+        <v>556691</v>
       </c>
       <c r="R20" t="n">
-        <v>7227107</v>
+        <v>7227079</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2617,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126091079</v>
+        <v>126091087</v>
       </c>
       <c r="B21" t="n">
-        <v>80147</v>
+        <v>80433</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2652,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556916</v>
+        <v>556869</v>
       </c>
       <c r="R21" t="n">
-        <v>7227278</v>
+        <v>7227096</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2682,12 +2683,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2718,10 +2719,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126091022</v>
+        <v>126091088</v>
       </c>
       <c r="B22" t="n">
-        <v>91371</v>
+        <v>80433</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2729,21 +2730,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2753,10 +2754,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557054</v>
+        <v>557057</v>
       </c>
       <c r="R22" t="n">
-        <v>7227356</v>
+        <v>7227107</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2783,12 +2784,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2819,10 +2820,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126091156</v>
+        <v>126091089</v>
       </c>
       <c r="B23" t="n">
-        <v>79043</v>
+        <v>80433</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2830,21 +2831,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2854,10 +2855,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>556815</v>
+        <v>557054</v>
       </c>
       <c r="R23" t="n">
-        <v>7227118</v>
+        <v>7227146</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2920,10 +2921,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126091109</v>
+        <v>126091026</v>
       </c>
       <c r="B24" t="n">
-        <v>80182</v>
+        <v>92632</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2931,21 +2932,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2955,10 +2956,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556865</v>
+        <v>556711</v>
       </c>
       <c r="R24" t="n">
-        <v>7227095</v>
+        <v>7227080</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,32 +3022,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126091048</v>
+        <v>126091142</v>
       </c>
       <c r="B25" t="n">
-        <v>80175</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3056,10 +3057,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556737</v>
+        <v>557156</v>
       </c>
       <c r="R25" t="n">
-        <v>7227086</v>
+        <v>7227270</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3122,53 +3123,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126091096</v>
+        <v>126091154</v>
       </c>
       <c r="B26" t="n">
-        <v>57684</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556986</v>
+        <v>556904</v>
       </c>
       <c r="R26" t="n">
-        <v>7227133</v>
+        <v>7227312</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3195,17 +3188,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3236,32 +3229,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126091094</v>
+        <v>126091155</v>
       </c>
       <c r="B27" t="n">
-        <v>80050</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3271,10 +3264,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556900</v>
+        <v>557073</v>
       </c>
       <c r="R27" t="n">
-        <v>7227075</v>
+        <v>7227326</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3301,12 +3294,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3337,14 +3330,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126091158</v>
+        <v>126091156</v>
       </c>
       <c r="B28" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3372,10 +3365,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556943</v>
+        <v>556815</v>
       </c>
       <c r="R28" t="n">
-        <v>7227059</v>
+        <v>7227118</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,32 +3431,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126091021</v>
+        <v>126091157</v>
       </c>
       <c r="B29" t="n">
-        <v>91371</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3473,10 +3466,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557035</v>
+        <v>556844</v>
       </c>
       <c r="R29" t="n">
-        <v>7227275</v>
+        <v>7227129</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3503,12 +3496,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3539,32 +3537,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126091078</v>
+        <v>126091158</v>
       </c>
       <c r="B30" t="n">
-        <v>80147</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3574,10 +3572,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556918</v>
+        <v>556943</v>
       </c>
       <c r="R30" t="n">
-        <v>7227271</v>
+        <v>7227059</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3604,12 +3602,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3640,32 +3638,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126091077</v>
+        <v>126091159</v>
       </c>
       <c r="B31" t="n">
-        <v>80147</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3675,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>556902</v>
+        <v>557055</v>
       </c>
       <c r="R31" t="n">
-        <v>7227281</v>
+        <v>7227102</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3705,12 +3703,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3741,32 +3739,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126091045</v>
+        <v>126091161</v>
       </c>
       <c r="B32" t="n">
-        <v>80175</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3776,10 +3774,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>556904</v>
+        <v>557149</v>
       </c>
       <c r="R32" t="n">
-        <v>7227312</v>
+        <v>7227169</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3806,12 +3804,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3842,10 +3845,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126091122</v>
+        <v>134287396</v>
       </c>
       <c r="B33" t="n">
-        <v>91731</v>
+        <v>79373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,37 +3856,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2063</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tallbacksmyrorna, Ås lm</t>
+          <t>tallbacksmyrorna (satellit), Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>556726</v>
+        <v>556997</v>
       </c>
       <c r="R33" t="n">
-        <v>7227064</v>
+        <v>7227372</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3907,12 +3910,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3927,48 +3940,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126091133</v>
+        <v>126091091</v>
       </c>
       <c r="B34" t="n">
-        <v>91389</v>
+        <v>80336</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3987,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556729</v>
+        <v>557022</v>
       </c>
       <c r="R34" t="n">
-        <v>7227082</v>
+        <v>7227286</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4008,12 +4017,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4044,10 +4053,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126091097</v>
+        <v>126091092</v>
       </c>
       <c r="B35" t="n">
-        <v>97373</v>
+        <v>80336</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4055,21 +4064,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221941</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4079,10 +4088,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>557160</v>
+        <v>556906</v>
       </c>
       <c r="R35" t="n">
-        <v>7227183</v>
+        <v>7227086</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,32 +4154,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126091131</v>
+        <v>126091094</v>
       </c>
       <c r="B36" t="n">
-        <v>91389</v>
+        <v>80336</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4180,10 +4189,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>556707</v>
+        <v>556900</v>
       </c>
       <c r="R36" t="n">
-        <v>7227095</v>
+        <v>7227075</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4246,10 +4255,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126091032</v>
+        <v>126091101</v>
       </c>
       <c r="B37" t="n">
-        <v>57684</v>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4257,42 +4266,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557048</v>
+        <v>556918</v>
       </c>
       <c r="R37" t="n">
-        <v>7227240</v>
+        <v>7227271</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4325,11 +4326,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4360,10 +4356,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126091060</v>
+        <v>126091102</v>
       </c>
       <c r="B38" t="n">
-        <v>80147</v>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4371,41 +4367,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>556945</v>
+        <v>556740</v>
       </c>
       <c r="R38" t="n">
-        <v>7227306</v>
+        <v>7227186</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4432,12 +4421,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4446,7 +4435,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4469,32 +4457,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126091108</v>
+        <v>126091103</v>
       </c>
       <c r="B39" t="n">
-        <v>80182</v>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4504,10 +4492,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>556916</v>
+        <v>556737</v>
       </c>
       <c r="R39" t="n">
-        <v>7227278</v>
+        <v>7227086</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4534,12 +4522,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4570,48 +4558,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126091110</v>
+        <v>134287393</v>
       </c>
       <c r="B40" t="n">
-        <v>80182</v>
+        <v>80488</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tallbacksmyrorna, Ås lm</t>
+          <t>tallbacksmyrorna (satellit), Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557049</v>
+        <v>557091</v>
       </c>
       <c r="R40" t="n">
-        <v>7227144</v>
+        <v>7227340</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4635,12 +4623,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4655,68 +4653,57 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126091061</v>
+        <v>126091045</v>
       </c>
       <c r="B41" t="n">
-        <v>80147</v>
+        <v>80461</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557049</v>
+        <v>556904</v>
       </c>
       <c r="R41" t="n">
-        <v>7227144</v>
+        <v>7227312</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4743,12 +4730,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4757,7 +4744,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4780,32 +4766,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126091011</v>
+        <v>126091046</v>
       </c>
       <c r="B42" t="n">
-        <v>79075</v>
+        <v>80461</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4815,10 +4801,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>557066</v>
+        <v>556915</v>
       </c>
       <c r="R42" t="n">
-        <v>7227351</v>
+        <v>7227293</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4881,32 +4867,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126091025</v>
+        <v>126091047</v>
       </c>
       <c r="B43" t="n">
-        <v>91371</v>
+        <v>80461</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4916,10 +4902,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>556986</v>
+        <v>556947</v>
       </c>
       <c r="R43" t="n">
-        <v>7227133</v>
+        <v>7227277</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4946,12 +4932,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4982,32 +4968,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126091101</v>
+        <v>126091048</v>
       </c>
       <c r="B44" t="n">
-        <v>80146</v>
+        <v>80461</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5017,10 +5003,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>556918</v>
+        <v>556737</v>
       </c>
       <c r="R44" t="n">
-        <v>7227271</v>
+        <v>7227086</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5047,12 +5033,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5086,7 +5072,7 @@
         <v>126091050</v>
       </c>
       <c r="B45" t="n">
-        <v>80175</v>
+        <v>80461</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5184,10 +5170,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126091111</v>
+        <v>126091170</v>
       </c>
       <c r="B46" t="n">
-        <v>80182</v>
+        <v>80467</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5195,21 +5181,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5219,10 +5205,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>557064</v>
+        <v>556915</v>
       </c>
       <c r="R46" t="n">
-        <v>7227147</v>
+        <v>7227293</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5249,12 +5235,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5285,32 +5271,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126091137</v>
+        <v>126091171</v>
       </c>
       <c r="B47" t="n">
-        <v>91389</v>
+        <v>80467</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5320,10 +5306,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>557054</v>
+        <v>557049</v>
       </c>
       <c r="R47" t="n">
-        <v>7227134</v>
+        <v>7227144</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5386,10 +5372,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126091113</v>
+        <v>126091446</v>
       </c>
       <c r="B48" t="n">
-        <v>57788</v>
+        <v>80467</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5397,21 +5383,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103031</v>
+        <v>6463</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5421,10 +5407,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>556728</v>
+        <v>556925</v>
       </c>
       <c r="R48" t="n">
-        <v>7227079</v>
+        <v>7227179</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5451,12 +5437,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5487,45 +5473,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126091142</v>
+        <v>126091009</v>
       </c>
       <c r="B49" t="n">
-        <v>79043</v>
+        <v>80468</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>557156</v>
+        <v>556917</v>
       </c>
       <c r="R49" t="n">
-        <v>7227270</v>
+        <v>7227275</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5552,12 +5541,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5566,6 +5555,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5588,53 +5578,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126091038</v>
+        <v>126091108</v>
       </c>
       <c r="B50" t="n">
-        <v>57684</v>
+        <v>80468</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557057</v>
+        <v>556916</v>
       </c>
       <c r="R50" t="n">
-        <v>7227134</v>
+        <v>7227278</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5661,17 +5643,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack färsk</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5702,52 +5679,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126091059</v>
+        <v>126091109</v>
       </c>
       <c r="B51" t="n">
-        <v>80147</v>
+        <v>80468</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>556914</v>
+        <v>556865</v>
       </c>
       <c r="R51" t="n">
-        <v>7227278</v>
+        <v>7227095</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5774,12 +5744,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5788,7 +5758,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5811,10 +5780,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126091171</v>
+        <v>126091110</v>
       </c>
       <c r="B52" t="n">
-        <v>80181</v>
+        <v>80468</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5822,21 +5791,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5912,53 +5881,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126091037</v>
+        <v>126091111</v>
       </c>
       <c r="B53" t="n">
-        <v>57684</v>
+        <v>80468</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>556702</v>
+        <v>557064</v>
       </c>
       <c r="R53" t="n">
-        <v>7227082</v>
+        <v>7227147</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5991,11 +5952,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6026,48 +5982,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126091353</v>
+        <v>134287421</v>
       </c>
       <c r="B54" t="n">
-        <v>98382</v>
+        <v>57886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221952</v>
+        <v>100011</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Tallbacksmyrorna, Ås lm</t>
+          <t>tallbacksmyrorna (satellit), Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>556926</v>
+        <v>556989</v>
       </c>
       <c r="R54" t="n">
-        <v>7227176</v>
+        <v>7227229</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6091,12 +6047,27 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>flög över huvudet</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6111,26 +6082,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126091161</v>
+        <v>126091030</v>
       </c>
       <c r="B55" t="n">
-        <v>79043</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6138,34 +6105,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>557149</v>
+        <v>557050</v>
       </c>
       <c r="R55" t="n">
-        <v>7227169</v>
+        <v>7227253</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6192,17 +6167,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Fertil</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6233,45 +6208,53 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126091026</v>
+        <v>126091032</v>
       </c>
       <c r="B56" t="n">
-        <v>92068</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>556711</v>
+        <v>557048</v>
       </c>
       <c r="R56" t="n">
-        <v>7227080</v>
+        <v>7227240</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6298,12 +6281,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6334,10 +6322,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126091134</v>
+        <v>126091035</v>
       </c>
       <c r="B57" t="n">
-        <v>91389</v>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6345,34 +6333,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>556726</v>
+        <v>557082</v>
       </c>
       <c r="R57" t="n">
-        <v>7227062</v>
+        <v>7227351</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6405,6 +6401,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6435,10 +6436,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126091139</v>
+        <v>126091037</v>
       </c>
       <c r="B58" t="n">
-        <v>91389</v>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6446,34 +6447,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>557138</v>
+        <v>556702</v>
       </c>
       <c r="R58" t="n">
-        <v>7227186</v>
+        <v>7227082</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6506,6 +6515,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6536,45 +6550,53 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126091054</v>
+        <v>126091038</v>
       </c>
       <c r="B59" t="n">
-        <v>98511</v>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>556704</v>
+        <v>557057</v>
       </c>
       <c r="R59" t="n">
-        <v>7227103</v>
+        <v>7227134</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6607,6 +6629,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack färsk</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6637,45 +6664,53 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126091057</v>
+        <v>126091039</v>
       </c>
       <c r="B60" t="n">
-        <v>98511</v>
+        <v>57953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>557065</v>
+        <v>557129</v>
       </c>
       <c r="R60" t="n">
-        <v>7227144</v>
+        <v>7227316</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6708,6 +6743,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6738,10 +6778,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126091035</v>
+        <v>126091096</v>
       </c>
       <c r="B61" t="n">
-        <v>57684</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6781,10 +6821,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>557082</v>
+        <v>556986</v>
       </c>
       <c r="R61" t="n">
-        <v>7227351</v>
+        <v>7227133</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6852,10 +6892,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126091082</v>
+        <v>126091116</v>
       </c>
       <c r="B62" t="n">
-        <v>80147</v>
+        <v>58116</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6863,21 +6903,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>103022</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6887,10 +6927,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>556947</v>
+        <v>556702</v>
       </c>
       <c r="R62" t="n">
-        <v>7227303</v>
+        <v>7227105</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6917,12 +6957,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6953,32 +6993,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126091091</v>
+        <v>126091117</v>
       </c>
       <c r="B63" t="n">
-        <v>80050</v>
+        <v>58116</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6456</v>
+        <v>103022</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6988,10 +7028,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>557022</v>
+        <v>556827</v>
       </c>
       <c r="R63" t="n">
-        <v>7227286</v>
+        <v>7227124</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7018,12 +7058,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7054,32 +7094,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126091446</v>
+        <v>126091118</v>
       </c>
       <c r="B64" t="n">
-        <v>80118</v>
+        <v>58116</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6463</v>
+        <v>103022</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7089,10 +7129,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>556925</v>
+        <v>556859</v>
       </c>
       <c r="R64" t="n">
-        <v>7227179</v>
+        <v>7227119</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7119,12 +7159,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7155,10 +7195,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126091116</v>
+        <v>126091112</v>
       </c>
       <c r="B65" t="n">
-        <v>57840</v>
+        <v>58057</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7166,21 +7206,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103022</v>
+        <v>103031</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7190,10 +7230,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>556702</v>
+        <v>556726</v>
       </c>
       <c r="R65" t="n">
-        <v>7227105</v>
+        <v>7227088</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7256,32 +7296,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126091056</v>
+        <v>126091113</v>
       </c>
       <c r="B66" t="n">
-        <v>98511</v>
+        <v>58057</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221952</v>
+        <v>103031</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7291,10 +7331,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>557140</v>
+        <v>556728</v>
       </c>
       <c r="R66" t="n">
-        <v>7227297</v>
+        <v>7227079</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7357,10 +7397,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126091136</v>
+        <v>126091115</v>
       </c>
       <c r="B67" t="n">
-        <v>91389</v>
+        <v>58057</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7368,21 +7408,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7392,10 +7432,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>556803</v>
+        <v>556797</v>
       </c>
       <c r="R67" t="n">
-        <v>7227106</v>
+        <v>7227252</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7422,12 +7462,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7458,10 +7498,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126091081</v>
+        <v>126091008</v>
       </c>
       <c r="B68" t="n">
-        <v>80147</v>
+        <v>56689</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7469,21 +7509,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>206046</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7493,10 +7533,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>556946</v>
+        <v>556848</v>
       </c>
       <c r="R68" t="n">
-        <v>7227279</v>
+        <v>7227178</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7529,6 +7569,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7559,32 +7604,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126091155</v>
+        <v>126091099</v>
       </c>
       <c r="B69" t="n">
-        <v>79043</v>
+        <v>99022</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7638,6 +7683,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7660,32 +7706,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126091086</v>
+        <v>126091097</v>
       </c>
       <c r="B70" t="n">
-        <v>80147</v>
+        <v>97989</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2081</v>
+        <v>221941</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7695,10 +7741,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>556691</v>
+        <v>557160</v>
       </c>
       <c r="R70" t="n">
-        <v>7227079</v>
+        <v>7227183</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7761,10 +7807,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126091046</v>
+        <v>126091054</v>
       </c>
       <c r="B71" t="n">
-        <v>80175</v>
+        <v>99140</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7772,21 +7818,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7796,10 +7842,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>556915</v>
+        <v>556704</v>
       </c>
       <c r="R71" t="n">
-        <v>7227293</v>
+        <v>7227103</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7826,12 +7872,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7862,32 +7908,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126091103</v>
+        <v>126091055</v>
       </c>
       <c r="B72" t="n">
-        <v>80146</v>
+        <v>99140</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7897,10 +7943,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>556737</v>
+        <v>556990</v>
       </c>
       <c r="R72" t="n">
-        <v>7227086</v>
+        <v>7227108</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7963,32 +8009,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126091154</v>
+        <v>126091056</v>
       </c>
       <c r="B73" t="n">
-        <v>79043</v>
+        <v>99140</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7998,10 +8044,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>556904</v>
+        <v>557140</v>
       </c>
       <c r="R73" t="n">
-        <v>7227312</v>
+        <v>7227297</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8028,17 +8074,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8069,48 +8110,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134287421</v>
+        <v>126091057</v>
       </c>
       <c r="B74" t="n">
-        <v>57886</v>
+        <v>99140</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100011</v>
+        <v>221952</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>tallbacksmyrorna (satellit), Ås lm</t>
+          <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>556989</v>
+        <v>557065</v>
       </c>
       <c r="R74" t="n">
-        <v>7227229</v>
+        <v>7227144</v>
       </c>
       <c r="S74" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8134,27 +8175,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>15:53</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>flög över huvudet</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8169,60 +8195,64 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134287393</v>
+        <v>126091058</v>
       </c>
       <c r="B75" t="n">
-        <v>80481</v>
+        <v>99140</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>tallbacksmyrorna (satellit), Ås lm</t>
+          <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>557091</v>
+        <v>557128</v>
       </c>
       <c r="R75" t="n">
-        <v>7227340</v>
+        <v>7227190</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8246,22 +8276,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8276,60 +8296,64 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134287396</v>
+        <v>126091353</v>
       </c>
       <c r="B76" t="n">
-        <v>79366</v>
+        <v>99140</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>tallbacksmyrorna (satellit), Ås lm</t>
+          <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>556997</v>
+        <v>556926</v>
       </c>
       <c r="R76" t="n">
-        <v>7227372</v>
+        <v>7227176</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8353,22 +8377,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>13:28</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>13:28</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8383,15 +8397,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
